--- a/prova_real/trimestre_04/resultado_T4.xlsx
+++ b/prova_real/trimestre_04/resultado_T4.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R60"/>
+  <dimension ref="A1:R57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -576,32 +576,32 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>MDNE3</t>
+          <t>HBOR3</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>54.8</v>
+        <v>61.3</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>10.12</v>
+        <v>15.51</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>27.64</v>
+        <v>35.8</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>5.49</v>
+        <v>0.45</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>29.1</v>
+        <v>16.27</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>-34.8064</v>
+        <v>-2.0168</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>12500</v>
+        <v>5882.35</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>3455</v>
+        <v>2105.88</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>15955</v>
+        <v>7988.24</v>
       </c>
     </row>
     <row r="3">
@@ -650,32 +650,32 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>HBOR3</t>
+          <t>MDNE3</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>61.3</v>
+        <v>54.8</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>13.68</v>
+        <v>12.2</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>27.2</v>
+        <v>22.55</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.5</v>
+        <v>5.06</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>18.37</v>
+        <v>26.49</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>-3.3895</v>
+        <v>-23.1772</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>12500</v>
+        <v>5882.35</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>3400</v>
+        <v>1326.47</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>15900</v>
+        <v>7208.82</v>
       </c>
     </row>
     <row r="4">
@@ -724,17 +724,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>VIVT3</t>
+          <t>DIRR3</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -743,13 +743,13 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>71</v>
+        <v>58.1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>4.83</v>
+        <v>13.13</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>23.96</v>
+        <v>18.37</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3.78</v>
+        <v>1.07</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>12.77</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>-5.4852</v>
+        <v>-4.0369</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>12500</v>
+        <v>5882.35</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>2995</v>
+        <v>1080.59</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>15495</v>
+        <v>6962.94</v>
       </c>
     </row>
     <row r="5">
@@ -798,17 +798,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PCAR3</t>
+          <t>CURY3</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -820,10 +820,10 @@
         <v>54.8</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>8.720000000000001</v>
+        <v>14.84</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>15.03</v>
+        <v>18.32</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -846,22 +846,22 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.27</v>
+        <v>0.89</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>8.76</v>
+        <v>3.3</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>-1.1064</v>
+        <v>0.3408</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>12500</v>
+        <v>5882.35</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>1878.75</v>
+        <v>1077.65</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>14378.75</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="6">
@@ -872,17 +872,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>DIRR3</t>
+          <t>VIVT3</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -891,13 +891,13 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>56.5</v>
+        <v>67.7</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>12.25</v>
+        <v>5.53</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>14.34</v>
+        <v>18.09</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -920,22 +920,22 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1.25</v>
+        <v>3.68</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>10.22</v>
+        <v>12.33</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>-9.0464</v>
+        <v>-5.1943</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>12500</v>
+        <v>5882.35</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>1792.5</v>
+        <v>1064.12</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>14292.5</v>
+        <v>6946.47</v>
       </c>
     </row>
     <row r="7">
@@ -946,32 +946,32 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>UNIP6</t>
+          <t>MELK3</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>11.79</v>
+        <v>10.89</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>7.38</v>
+        <v>17.9</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -994,22 +994,22 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2.19</v>
+        <v>0.09</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>4.49</v>
+        <v>3.01</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>-0.6077</v>
+        <v>0.3674</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>12500</v>
+        <v>5882.35</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>922.5</v>
+        <v>1052.94</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>13422.5</v>
+        <v>6935.29</v>
       </c>
     </row>
     <row r="8">
@@ -1020,17 +1020,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>CYRE3</t>
+          <t>PCAR3</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1042,10 +1042,10 @@
         <v>54.8</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>12.92</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>3.92</v>
+        <v>17.55</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -1068,22 +1068,22 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.99</v>
+        <v>0.27</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>4.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>-4.3031</v>
+        <v>-0.9192</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>12500</v>
+        <v>5882.35</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>490</v>
+        <v>1032.35</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>12990</v>
+        <v>6914.71</v>
       </c>
     </row>
     <row r="9">
@@ -1094,17 +1094,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>TEND3</t>
+          <t>LAVV3</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1116,10 +1116,10 @@
         <v>54.8</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>10.17</v>
+        <v>15.7</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>-5.4</v>
+        <v>15.17</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -1128,997 +1128,997 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>✅ COMPRAR</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>-5.7708</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>5882.35</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>892.35</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>6774.71</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>MYPK3</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>✅ COMPRAR</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>-0.3251</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>5882.35</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>873.53</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>6755.88</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>UNIP6</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>✅ COMPRAR</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>-0.2974</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>5882.35</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>732.35</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>6614.71</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>CYRE3</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>✅ COMPRAR</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>-4.2561</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>5882.35</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>647.65</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>6530</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>ALPA4</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>✅ COMPRAR</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>-2.5787</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>5882.35</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>334.71</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>6217.06</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>ITUB3</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>✅ COMPRAR</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>-0.7497</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>5882.35</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>287.06</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>6169.41</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>TEND3</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>✅ COMPRAR</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>-13.0898</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>5882.35</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>85.29000000000001</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>5967.65</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>TOTS3</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>✅ COMPRAR</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>-1.6474</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>5882.35</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>64.70999999999999</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>5947.06</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>QUEDA</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>❌ NÃO</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>✅ COMPRAR</t>
         </is>
       </c>
-      <c r="M9" s="2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>21.32</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>-18.3283</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>12500</v>
-      </c>
-      <c r="Q9" s="2" t="n">
-        <v>-675</v>
-      </c>
-      <c r="R9" s="2" t="n">
-        <v>11825</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>T-4</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>CURY3</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="M17" s="2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>-10.989</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>5882.35</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>-357.06</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>5525.29</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>BBSE3</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>-6.91</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>❌ NÃO</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>✅ COMPRAR</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>-83.3188</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>5882.35</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>-406.47</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>5475.88</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>MULT3</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Pouco Previsível</t>
         </is>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>53.2</v>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>13.98</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>13.03</v>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="G19" s="3" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>⚠️ OBSERVAR</t>
         </is>
       </c>
-      <c r="M10" s="3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.2502</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>T-4</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>MYPK3</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="M19" s="3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>-5.6892</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>CGRA4</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Pouco Previsível</t>
         </is>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>53.2</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>9.109999999999999</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="G20" s="3" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>⚠️ OBSERVAR</t>
         </is>
       </c>
-      <c r="M11" s="3" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>0.1828</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>T-4</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>CGRA4</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="M20" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>-1.4266</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>SANB11</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Pouco Previsível</t>
         </is>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>53.2</v>
       </c>
-      <c r="G12" s="3" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="G21" s="3" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>-2.66</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>❌ NÃO</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>⚠️ OBSERVAR</t>
         </is>
       </c>
-      <c r="M12" s="3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="O12" s="3" t="n">
-        <v>-1.0338</v>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>T-4</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>PSSA3</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="M21" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>-1.9873</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IRBR3</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Pouco Previsível</t>
         </is>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>53.2</v>
       </c>
-      <c r="G13" s="3" t="n">
-        <v>9.15</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="G22" s="3" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>-3.26</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>❌ NÃO</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>⚠️ OBSERVAR</t>
         </is>
       </c>
-      <c r="M13" s="3" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>13.69</v>
-      </c>
-      <c r="O13" s="3" t="n">
-        <v>-29.8778</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>T-4</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>ITUB3</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Pouco Previsível</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>10.59</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ OBSERVAR</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>-1.3603</v>
-      </c>
-      <c r="P14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>T-4</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>TOTS3</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Pouco Previsível</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>13.69</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>-2.02</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>❌ NÃO</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ OBSERVAR</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="O15" s="3" t="n">
-        <v>-2.2548</v>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>T-4</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>LIGT3</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Pouco Previsível</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>6.53</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>❌ NÃO</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ OBSERVAR</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>20.08</v>
-      </c>
-      <c r="O16" s="3" t="n">
-        <v>-7.4075</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>T-4</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IRBR3</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Pouco Previsível</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>-3.45</v>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>❌ NÃO</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>⚠️ OBSERVAR</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="N17" s="3" t="n">
+      <c r="M22" s="3" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="N22" s="3" t="n">
         <v>14.37</v>
       </c>
-      <c r="O17" s="3" t="n">
-        <v>-13.547</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>T-4</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>MDIA3</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>Pouco Previsível</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="N18" s="4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O18" s="4" t="n">
-        <v>-0.3033</v>
-      </c>
-      <c r="P18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>T-4</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>ODPV3</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>Pouco Previsível</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>19.24</v>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="N19" s="4" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="O19" s="4" t="n">
-        <v>-1.1734</v>
-      </c>
-      <c r="P19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>T-4</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>SAUD3</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>Pouco Previsível</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>19.24</v>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="N20" s="4" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="O20" s="4" t="n">
-        <v>-1.1734</v>
-      </c>
-      <c r="P20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>T-4</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>FLRY3</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>-3.75</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>12.77</v>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>❌ NÃO</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v>15.24</v>
-      </c>
-      <c r="O21" s="4" t="n">
-        <v>-8.722099999999999</v>
-      </c>
-      <c r="P21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>T-4</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>GGPS3</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>-7.91</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>❌ NÃO</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v>15.39</v>
-      </c>
-      <c r="O22" s="4" t="n">
-        <v>-10.6832</v>
-      </c>
-      <c r="P22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="4" t="n">
+      <c r="O22" s="3" t="n">
+        <v>-14.3132</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2130,36 +2130,36 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>LWSA3</t>
+          <t>MDIA3</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>53.2</v>
+        <v>54.8</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-13.9</v>
+        <v>3.56</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>6.65</v>
+        <v>27.31</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -2178,13 +2178,13 @@
         </is>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.14</v>
+        <v>1.55</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>30.75</v>
+        <v>5.83</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-62.0082</v>
+        <v>-0.2127</v>
       </c>
       <c r="P23" s="4" t="n">
         <v>0</v>
@@ -2204,36 +2204,36 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>GGBR4</t>
+          <t>ODPV3</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>53.2</v>
+        <v>54.8</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-13.66</v>
+        <v>1.97</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>5.68</v>
+        <v>22.63</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -2252,13 +2252,13 @@
         </is>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.61</v>
+        <v>0.88</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>16.34</v>
+        <v>7.39</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-37.7673</v>
+        <v>-1.3052</v>
       </c>
       <c r="P24" s="4" t="n">
         <v>0</v>
@@ -2278,36 +2278,36 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CMIG4</t>
+          <t>SAUD3</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>53.2</v>
+        <v>54.8</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.13</v>
+        <v>1.97</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.64</v>
+        <v>22.63</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -2326,13 +2326,13 @@
         </is>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>7.29</v>
+        <v>7.39</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-10.5309</v>
+        <v>-1.3052</v>
       </c>
       <c r="P25" s="4" t="n">
         <v>0</v>
@@ -2352,36 +2352,36 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>GGBR3</t>
+          <t>MILS3</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>54.8</v>
+        <v>53.2</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-12.89</v>
+        <v>3.78</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.62</v>
+        <v>19.08</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -2400,13 +2400,13 @@
         </is>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.57</v>
+        <v>1.12</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>10.99</v>
+        <v>11.18</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-29.5595</v>
+        <v>-4.161</v>
       </c>
       <c r="P26" s="4" t="n">
         <v>0</v>
@@ -2426,32 +2426,32 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>CEED4</t>
+          <t>BEEF3</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>100</v>
+        <v>53.2</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0</v>
+        <v>17.35</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0</v>
+        <v>10.56</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1</v>
+        <v>-2.677</v>
       </c>
       <c r="P27" s="4" t="n">
         <v>0</v>
@@ -2500,32 +2500,32 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>PRIO3</t>
+          <t>GGPS3</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>53.2</v>
+        <v>59.7</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-5.87</v>
+        <v>-6.49</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-2.6</v>
+        <v>16.62</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -2548,13 +2548,13 @@
         </is>
       </c>
       <c r="M28" s="4" t="n">
-        <v>5.76</v>
+        <v>1.97</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>13.81</v>
+        <v>14.16</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-9.4702</v>
+        <v>-7.507</v>
       </c>
       <c r="P28" s="4" t="n">
         <v>0</v>
@@ -2574,32 +2574,32 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>KLBN11</t>
+          <t>FLRY3</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>53.2</v>
+        <v>56.5</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-7.3</v>
+        <v>-2.52</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-2.89</v>
+        <v>16.39</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.6</v>
+        <v>1.83</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.53</v>
+        <v>14.23</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.2958</v>
+        <v>-7.1763</v>
       </c>
       <c r="P29" s="4" t="n">
         <v>0</v>
@@ -2648,41 +2648,41 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>AERI3</t>
+          <t>EVEN3</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>54.8</v>
+        <v>53.2</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-34.69</v>
+        <v>3.82</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-3.04</v>
+        <v>7.98</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
@@ -2696,13 +2696,13 @@
         </is>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.05</v>
+        <v>0.74</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>24.58</v>
+        <v>11.5</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-64.23220000000001</v>
+        <v>-16.3579</v>
       </c>
       <c r="P30" s="4" t="n">
         <v>0</v>
@@ -2722,32 +2722,32 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>LOGN3</t>
+          <t>GGBR3</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>54.8</v>
+        <v>53.2</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.42</v>
+        <v>-13.56</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-4.29</v>
+        <v>1.96</v>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
@@ -2756,12 +2756,12 @@
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2770,13 +2770,13 @@
         </is>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.14</v>
+        <v>1.74</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>16.14</v>
+        <v>12.15</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-56.3705</v>
+        <v>-35.7869</v>
       </c>
       <c r="P31" s="4" t="n">
         <v>0</v>
@@ -2796,41 +2796,41 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>CAMB3</t>
+          <t>EGIE3</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>54.8</v>
+        <v>53.2</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-7.09</v>
+        <v>3.17</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-4.54</v>
+        <v>0.46</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -2844,13 +2844,13 @@
         </is>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.55</v>
+        <v>1.4</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>6.37</v>
+        <v>4.72</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-4.0434</v>
+        <v>-1.1208</v>
       </c>
       <c r="P32" s="4" t="n">
         <v>0</v>
@@ -2870,41 +2870,41 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>CAML3</t>
+          <t>CEED4</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>53.2</v>
+        <v>100</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-54.54</v>
+        <v>0</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-5.27</v>
+        <v>0</v>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>QUEDA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>52.84</v>
+        <v>0</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-69.16070000000001</v>
+        <v>1</v>
       </c>
       <c r="P33" s="4" t="n">
         <v>0</v>
@@ -2944,17 +2944,17 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>SBFG3</t>
+          <t>SIMH3</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -2966,24 +2966,24 @@
         <v>53.2</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-7.97</v>
+        <v>1.9</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-7.81</v>
+        <v>-1.33</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
           <t>QUEDA</t>
         </is>
       </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2992,13 +2992,13 @@
         </is>
       </c>
       <c r="M34" s="4" t="n">
-        <v>1.79</v>
+        <v>1.03</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>15.82</v>
+        <v>9.85</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-6.1269</v>
+        <v>-0.8437</v>
       </c>
       <c r="P34" s="4" t="n">
         <v>0</v>
@@ -3018,17 +3018,17 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>KEPL3</t>
+          <t>PRIO3</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -3040,10 +3040,10 @@
         <v>53.2</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-13.41</v>
+        <v>-5.43</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-9.82</v>
+        <v>-2.92</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
@@ -3066,13 +3066,13 @@
         </is>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.78</v>
+        <v>5.5</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>10.57</v>
+        <v>13.18</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-2.4103</v>
+        <v>-7.8478</v>
       </c>
       <c r="P35" s="4" t="n">
         <v>0</v>
@@ -3092,32 +3092,32 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>DMVF3</t>
+          <t>CSNA3</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>54.8</v>
+        <v>58.1</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-7.77</v>
+        <v>-11.15</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-10.17</v>
+        <v>-6.19</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
@@ -3140,13 +3140,13 @@
         </is>
       </c>
       <c r="M36" s="4" t="n">
-        <v>0.37</v>
+        <v>0.31</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>7.73</v>
+        <v>4.05</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>-1.0069</v>
+        <v>0.4061</v>
       </c>
       <c r="P36" s="4" t="n">
         <v>0</v>
@@ -3171,27 +3171,27 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>56.5</v>
+        <v>53.2</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-1.81</v>
+        <v>-2.31</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-11.56</v>
+        <v>-7.01</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
@@ -3214,13 +3214,13 @@
         </is>
       </c>
       <c r="M37" s="4" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>7.81</v>
+        <v>7.37</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>-2.6774</v>
+        <v>-2.2774</v>
       </c>
       <c r="P37" s="4" t="n">
         <v>0</v>
@@ -3240,32 +3240,32 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>RECV3</t>
+          <t>SBFG3</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>61.3</v>
+        <v>53.2</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-6.17</v>
+        <v>-6.42</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-12.02</v>
+        <v>-8.94</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
@@ -3288,13 +3288,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.72</v>
+        <v>1.52</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>5.59</v>
+        <v>13.47</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-0.2511</v>
+        <v>-4.222</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>0</v>
@@ -3314,32 +3314,32 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>ARML3</t>
+          <t>RECV3</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>54.8</v>
+        <v>58.1</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-44.14</v>
+        <v>-6.1</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-14.82</v>
+        <v>-9.31</v>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="M39" s="4" t="n">
-        <v>1.2</v>
+        <v>0.65</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>33.32</v>
+        <v>5.08</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>-5.8901</v>
+        <v>-0.0747</v>
       </c>
       <c r="P39" s="4" t="n">
         <v>0</v>
@@ -3388,17 +3388,17 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>WEGE3</t>
+          <t>USIM3</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -3410,10 +3410,10 @@
         <v>54.8</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-13.05</v>
+        <v>-4.73</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-14.92</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M40" s="4" t="n">
-        <v>1.27</v>
+        <v>0.77</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>3.44</v>
+        <v>17.73</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>0.6066</v>
+        <v>-6.1553</v>
       </c>
       <c r="P40" s="4" t="n">
         <v>0</v>
@@ -3462,17 +3462,17 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>DESK3</t>
+          <t>QUAL3</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -3484,10 +3484,10 @@
         <v>53.2</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>-31.14</v>
+        <v>-2.48</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>-15.52</v>
+        <v>-10.16</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
@@ -3510,13 +3510,13 @@
         </is>
       </c>
       <c r="M41" s="4" t="n">
-        <v>2.45</v>
+        <v>0.13</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>28.16</v>
+        <v>7.19</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>-10.8614</v>
+        <v>-0.1581</v>
       </c>
       <c r="P41" s="4" t="n">
         <v>0</v>
@@ -3536,32 +3536,32 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>USIM3</t>
+          <t>BRKM5</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-4.59</v>
+        <v>-28.32</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>-15.56</v>
+        <v>-10.54</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
@@ -3584,13 +3584,13 @@
         </is>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.77</v>
+        <v>1.05</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>17.58</v>
+        <v>11.36</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>-4.9347</v>
+        <v>-0.9533</v>
       </c>
       <c r="P42" s="4" t="n">
         <v>0</v>
@@ -3610,32 +3610,32 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>INTB3</t>
+          <t>AGXY3</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>54.8</v>
+        <v>53.2</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>-14.49</v>
+        <v>-1.39</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>-15.7</v>
+        <v>-11.27</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
@@ -3658,13 +3658,13 @@
         </is>
       </c>
       <c r="M43" s="4" t="n">
-        <v>2.94</v>
+        <v>1.55</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>22</v>
+        <v>25.64</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>-8.9023</v>
+        <v>-70.6908</v>
       </c>
       <c r="P43" s="4" t="n">
         <v>0</v>
@@ -3684,32 +3684,32 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>QUAL3</t>
+          <t>DESK3</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F44" s="4" t="n">
-        <v>56.5</v>
+        <v>53.2</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>-3.49</v>
+        <v>-29.49</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>-16.11</v>
+        <v>-11.5</v>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.12</v>
+        <v>2.28</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>6.5</v>
+        <v>26.32</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>0.1371</v>
+        <v>-9.265700000000001</v>
       </c>
       <c r="P44" s="4" t="n">
         <v>0</v>
@@ -3758,17 +3758,17 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>JSLG3</t>
+          <t>INTB3</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -3780,10 +3780,10 @@
         <v>53.2</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>-4.42</v>
+        <v>-11.48</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>-16.22</v>
+        <v>-11.78</v>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
@@ -3806,13 +3806,13 @@
         </is>
       </c>
       <c r="M45" s="4" t="n">
-        <v>0.22</v>
+        <v>2.42</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>5.19</v>
+        <v>18.1</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>0.2614</v>
+        <v>-5.049</v>
       </c>
       <c r="P45" s="4" t="n">
         <v>0</v>
@@ -3832,32 +3832,32 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>CSNA3</t>
+          <t>DMVF3</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>62.9</v>
+        <v>54.8</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>-11.52</v>
+        <v>-8</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>-16.49</v>
+        <v>-11.79</v>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
@@ -3880,13 +3880,13 @@
         </is>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>4</v>
+        <v>7.59</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>0.4487</v>
+        <v>-1.2259</v>
       </c>
       <c r="P46" s="4" t="n">
         <v>0</v>
@@ -3906,32 +3906,32 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>AGXY3</t>
+          <t>USIM5</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>54.8</v>
+        <v>53.2</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>-0.43</v>
+        <v>-5.25</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>-17.59</v>
+        <v>-14.48</v>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="M47" s="4" t="n">
-        <v>1.66</v>
+        <v>0.84</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>27.3</v>
+        <v>19.9</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>-65.03530000000001</v>
+        <v>-4.9031</v>
       </c>
       <c r="P47" s="4" t="n">
         <v>0</v>
@@ -3980,17 +3980,17 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>AZZA3</t>
+          <t>ARML3</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -4002,10 +4002,10 @@
         <v>54.8</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>-10.37</v>
+        <v>-40.34</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>-20.07</v>
+        <v>-17.63</v>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
@@ -4028,13 +4028,13 @@
         </is>
       </c>
       <c r="M48" s="4" t="n">
-        <v>9.609999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>27.29</v>
+        <v>29.65</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>-7.7481</v>
+        <v>-5.2341</v>
       </c>
       <c r="P48" s="4" t="n">
         <v>0</v>
@@ -4054,32 +4054,32 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>USIM5</t>
+          <t>RAIL3</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F49" s="4" t="n">
-        <v>56.5</v>
+        <v>53.2</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>-5.21</v>
+        <v>-3.6</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>-21.09</v>
+        <v>-20.47</v>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
@@ -4102,13 +4102,13 @@
         </is>
       </c>
       <c r="M49" s="4" t="n">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>19.28</v>
+        <v>5.66</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>-3.6991</v>
+        <v>0.1428</v>
       </c>
       <c r="P49" s="4" t="n">
         <v>0</v>
@@ -4128,32 +4128,32 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>RAPT4</t>
+          <t>AZZA3</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F50" s="4" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-12.25</v>
+        <v>-7</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>-23.17</v>
+        <v>-22.78</v>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
@@ -4176,13 +4176,13 @@
         </is>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0.72</v>
+        <v>7.8</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>8.91</v>
+        <v>22.23</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>0.3674</v>
+        <v>-5.3449</v>
       </c>
       <c r="P50" s="4" t="n">
         <v>0</v>
@@ -4202,17 +4202,17 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>DASA3</t>
+          <t>TUPY3</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="F51" s="4" t="n">
-        <v>56.5</v>
+        <v>59.7</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>-21.4</v>
+        <v>-5.37</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>-23.46</v>
+        <v>-23.11</v>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
@@ -4250,13 +4250,13 @@
         </is>
       </c>
       <c r="M51" s="4" t="n">
-        <v>0.09</v>
+        <v>1.88</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>6.48</v>
+        <v>11.81</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>0.2827</v>
+        <v>-1.1715</v>
       </c>
       <c r="P51" s="4" t="n">
         <v>0</v>
@@ -4276,17 +4276,17 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>TUPY3</t>
+          <t>JALL3</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -4295,13 +4295,13 @@
         </is>
       </c>
       <c r="F52" s="4" t="n">
-        <v>59.7</v>
+        <v>58.1</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-5.37</v>
+        <v>-20.04</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>-25</v>
+        <v>-24.69</v>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
@@ -4324,13 +4324,13 @@
         </is>
       </c>
       <c r="M52" s="4" t="n">
-        <v>1.69</v>
+        <v>0.29</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>10.52</v>
+        <v>7.87</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>-0.8956</v>
+        <v>0.4634</v>
       </c>
       <c r="P52" s="4" t="n">
         <v>0</v>
@@ -4350,32 +4350,32 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>BRKM5</t>
+          <t>RAPT4</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F53" s="4" t="n">
-        <v>58.1</v>
+        <v>54.8</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>-30.88</v>
+        <v>-11.59</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>-25.45</v>
+        <v>-25.61</v>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
@@ -4398,13 +4398,13 @@
         </is>
       </c>
       <c r="M53" s="4" t="n">
-        <v>1.37</v>
+        <v>0.71</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>14.76</v>
+        <v>9.01</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>-1.2485</v>
+        <v>0.4216</v>
       </c>
       <c r="P53" s="4" t="n">
         <v>0</v>
@@ -4424,32 +4424,32 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>FHER3</t>
+          <t>CSAN3</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F54" s="4" t="n">
-        <v>53.2</v>
+        <v>62.9</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>-10.68</v>
+        <v>-26.62</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>-30.73</v>
+        <v>-28.94</v>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
@@ -4472,13 +4472,13 @@
         </is>
       </c>
       <c r="M54" s="4" t="n">
-        <v>0.33</v>
+        <v>0.98</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>7.48</v>
+        <v>14.2</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>-0.3467</v>
+        <v>-0.3011</v>
       </c>
       <c r="P54" s="4" t="n">
         <v>0</v>
@@ -4498,17 +4498,17 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>JALL3</t>
+          <t>TASA4</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -4517,13 +4517,13 @@
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>58.1</v>
+        <v>56.5</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>-21.59</v>
+        <v>-4.77</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>-32.27</v>
+        <v>-38.7</v>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
@@ -4546,13 +4546,13 @@
         </is>
       </c>
       <c r="M55" s="4" t="n">
-        <v>0.36</v>
+        <v>1.15</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>9.449999999999999</v>
+        <v>23.07</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>0.1805</v>
+        <v>-0.9275</v>
       </c>
       <c r="P55" s="4" t="n">
         <v>0</v>
@@ -4572,17 +4572,17 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>CSAN3</t>
+          <t>RAIZ4</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -4597,7 +4597,7 @@
         <v>-29.56</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>-33.78</v>
+        <v>-43.23</v>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
@@ -4620,13 +4620,13 @@
         </is>
       </c>
       <c r="M56" s="4" t="n">
-        <v>1.3</v>
+        <v>0.23</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>18.84</v>
+        <v>14.33</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>-0.8971</v>
+        <v>0.1477</v>
       </c>
       <c r="P56" s="4" t="n">
         <v>0</v>
@@ -4646,32 +4646,32 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>CBAV3</t>
+          <t>GFSA3</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>53.2</v>
+        <v>64.5</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>-16.97</v>
+        <v>-0.92</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>-36.61</v>
+        <v>-47.46</v>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
@@ -4694,13 +4694,13 @@
         </is>
       </c>
       <c r="M57" s="4" t="n">
-        <v>0.59</v>
+        <v>8.81</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>13.8</v>
+        <v>54.2</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>-0.0984</v>
+        <v>-4.9531</v>
       </c>
       <c r="P57" s="4" t="n">
         <v>0</v>
@@ -4709,228 +4709,6 @@
         <v>0</v>
       </c>
       <c r="R57" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>T-4</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>TASA4</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="G58" s="4" t="n">
-        <v>-5.72</v>
-      </c>
-      <c r="H58" s="4" t="n">
-        <v>-39.49</v>
-      </c>
-      <c r="I58" s="4" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="K58" s="4" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M58" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N58" s="4" t="n">
-        <v>19.75</v>
-      </c>
-      <c r="O58" s="4" t="n">
-        <v>-0.4542</v>
-      </c>
-      <c r="P58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>T-4</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>GFSA3</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="G59" s="4" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="H59" s="4" t="n">
-        <v>-42.67</v>
-      </c>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="K59" s="4" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M59" s="4" t="n">
-        <v>8.24</v>
-      </c>
-      <c r="N59" s="4" t="n">
-        <v>49.49</v>
-      </c>
-      <c r="O59" s="4" t="n">
-        <v>-4.3069</v>
-      </c>
-      <c r="P59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>T-4</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>RAIZ4</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="G60" s="4" t="n">
-        <v>-32.44</v>
-      </c>
-      <c r="H60" s="4" t="n">
-        <v>-46.7</v>
-      </c>
-      <c r="I60" s="4" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="K60" s="4" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M60" s="4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N60" s="4" t="n">
-        <v>18.06</v>
-      </c>
-      <c r="O60" s="4" t="n">
-        <v>-0.3542</v>
-      </c>
-      <c r="P60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4945,7 +4723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5068,32 +4846,32 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>MDNE3</t>
+          <t>HBOR3</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>54.8</v>
+        <v>61.3</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>10.12</v>
+        <v>15.51</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>27.64</v>
+        <v>35.8</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -5116,22 +4894,22 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>5.49</v>
+        <v>0.45</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>29.1</v>
+        <v>16.27</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>-34.8064</v>
+        <v>-2.0168</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>12500</v>
+        <v>5882.35</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>3455</v>
+        <v>2105.88</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>15955</v>
+        <v>7988.24</v>
       </c>
     </row>
     <row r="3">
@@ -5142,32 +4920,32 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>HBOR3</t>
+          <t>MDNE3</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>61.3</v>
+        <v>54.8</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>13.68</v>
+        <v>12.2</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>27.2</v>
+        <v>22.55</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -5190,22 +4968,22 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.5</v>
+        <v>5.06</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>18.37</v>
+        <v>26.49</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>-3.3895</v>
+        <v>-23.1772</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>12500</v>
+        <v>5882.35</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>3400</v>
+        <v>1326.47</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>15900</v>
+        <v>7208.82</v>
       </c>
     </row>
     <row r="4">
@@ -5216,17 +4994,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>VIVT3</t>
+          <t>DIRR3</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -5235,13 +5013,13 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>71</v>
+        <v>58.1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>4.83</v>
+        <v>13.13</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>23.96</v>
+        <v>18.37</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -5264,22 +5042,22 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3.78</v>
+        <v>1.07</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>12.77</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>-5.4852</v>
+        <v>-4.0369</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>12500</v>
+        <v>5882.35</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>2995</v>
+        <v>1080.59</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>15495</v>
+        <v>6962.94</v>
       </c>
     </row>
     <row r="5">
@@ -5290,17 +5068,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PCAR3</t>
+          <t>CURY3</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -5312,10 +5090,10 @@
         <v>54.8</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>8.720000000000001</v>
+        <v>14.84</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>15.03</v>
+        <v>18.32</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -5338,22 +5116,22 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.27</v>
+        <v>0.89</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>8.76</v>
+        <v>3.3</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>-1.1064</v>
+        <v>0.3408</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>12500</v>
+        <v>5882.35</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>1878.75</v>
+        <v>1077.65</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>14378.75</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="6">
@@ -5364,17 +5142,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>DIRR3</t>
+          <t>VIVT3</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -5383,13 +5161,13 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>56.5</v>
+        <v>67.7</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>12.25</v>
+        <v>5.53</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>14.34</v>
+        <v>18.09</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -5412,22 +5190,22 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1.25</v>
+        <v>3.68</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>10.22</v>
+        <v>12.33</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>-9.0464</v>
+        <v>-5.1943</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>12500</v>
+        <v>5882.35</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>1792.5</v>
+        <v>1064.12</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>14292.5</v>
+        <v>6946.47</v>
       </c>
     </row>
     <row r="7">
@@ -5438,32 +5216,32 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>UNIP6</t>
+          <t>MELK3</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>11.79</v>
+        <v>10.89</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>7.38</v>
+        <v>17.9</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -5486,22 +5264,22 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2.19</v>
+        <v>0.09</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>4.49</v>
+        <v>3.01</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>-0.6077</v>
+        <v>0.3674</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>12500</v>
+        <v>5882.35</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>922.5</v>
+        <v>1052.94</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>13422.5</v>
+        <v>6935.29</v>
       </c>
     </row>
     <row r="8">
@@ -5512,17 +5290,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>CYRE3</t>
+          <t>PCAR3</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -5534,10 +5312,10 @@
         <v>54.8</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>12.92</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>3.92</v>
+        <v>17.55</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -5560,22 +5338,22 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.99</v>
+        <v>0.27</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>4.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>-4.3031</v>
+        <v>-0.9192</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>12500</v>
+        <v>5882.35</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>490</v>
+        <v>1032.35</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>12990</v>
+        <v>6914.71</v>
       </c>
     </row>
     <row r="9">
@@ -5586,17 +5364,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>TEND3</t>
+          <t>LAVV3</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -5608,10 +5386,10 @@
         <v>54.8</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>10.17</v>
+        <v>15.7</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>-5.4</v>
+        <v>15.17</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -5620,36 +5398,702 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>✅ COMPRAR</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>-5.7708</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>5882.35</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>892.35</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>6774.71</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>MYPK3</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>✅ COMPRAR</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>-0.3251</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>5882.35</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>873.53</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>6755.88</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>UNIP6</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>12.45</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>✅ COMPRAR</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>-0.2974</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>5882.35</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>732.35</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>6614.71</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>CYRE3</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>✅ COMPRAR</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>-4.2561</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>5882.35</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>647.65</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>6530</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>ALPA4</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>✅ COMPRAR</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>-2.5787</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>5882.35</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>334.71</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>6217.06</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>ITUB3</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>✅ COMPRAR</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>-0.7497</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>5882.35</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>287.06</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>6169.41</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>TEND3</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>✅ COMPRAR</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>-13.0898</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>5882.35</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>85.29000000000001</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>5967.65</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>TOTS3</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Muito Previsível</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>✅ SIM</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>✅ COMPRAR</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>-1.6474</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>5882.35</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>64.70999999999999</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>5947.06</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SLCE3</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>QUEDA</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>❌ NÃO</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>✅ COMPRAR</t>
         </is>
       </c>
-      <c r="M9" s="2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>21.32</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>-18.3283</v>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>12500</v>
-      </c>
-      <c r="Q9" s="2" t="n">
-        <v>-675</v>
-      </c>
-      <c r="R9" s="2" t="n">
-        <v>11825</v>
+      <c r="M17" s="2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>-10.989</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>5882.35</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>-357.06</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>5525.29</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>T-4</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>BBSE3</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Previsibilidade Moderada</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>-6.91</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>❌ NÃO</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>✅ COMPRAR</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>-83.3188</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>5882.35</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>-406.47</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>5475.88</v>
       </c>
     </row>
   </sheetData>
